--- a/artfynd/A 62725-2023 artfynd.xlsx
+++ b/artfynd/A 62725-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133230125</v>
       </c>
       <c r="B2" t="n">
-        <v>101386</v>
+        <v>101403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
